--- a/artfynd/A 60484-2024 artfynd.xlsx
+++ b/artfynd/A 60484-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124464179</v>
+        <v>124464175</v>
       </c>
       <c r="B2" t="n">
-        <v>91172</v>
+        <v>78546</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1503</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>878958</v>
+        <v>878975</v>
       </c>
       <c r="R2" t="n">
-        <v>7377740</v>
+        <v>7377725</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124464181</v>
+        <v>124464173</v>
       </c>
       <c r="B3" t="n">
-        <v>78810</v>
+        <v>92490</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>878962</v>
+        <v>879013</v>
       </c>
       <c r="R3" t="n">
-        <v>7377739</v>
+        <v>7377725</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124464175</v>
+        <v>124464181</v>
       </c>
       <c r="B4" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>878975</v>
+        <v>878962</v>
       </c>
       <c r="R4" t="n">
-        <v>7377725</v>
+        <v>7377739</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124464173</v>
+        <v>124464179</v>
       </c>
       <c r="B5" t="n">
-        <v>92490</v>
+        <v>91172</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2079</v>
+        <v>1503</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>879013</v>
+        <v>878958</v>
       </c>
       <c r="R5" t="n">
-        <v>7377725</v>
+        <v>7377740</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>

--- a/artfynd/A 60484-2024 artfynd.xlsx
+++ b/artfynd/A 60484-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124464175</v>
+        <v>124464181</v>
       </c>
       <c r="B2" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>878975</v>
+        <v>878962</v>
       </c>
       <c r="R2" t="n">
-        <v>7377725</v>
+        <v>7377739</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124464173</v>
+        <v>124464179</v>
       </c>
       <c r="B3" t="n">
-        <v>92490</v>
+        <v>91172</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2079</v>
+        <v>1503</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>879013</v>
+        <v>878958</v>
       </c>
       <c r="R3" t="n">
-        <v>7377725</v>
+        <v>7377740</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124464181</v>
+        <v>124464173</v>
       </c>
       <c r="B4" t="n">
-        <v>78810</v>
+        <v>92490</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>878962</v>
+        <v>879013</v>
       </c>
       <c r="R4" t="n">
-        <v>7377739</v>
+        <v>7377725</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124464179</v>
+        <v>124464175</v>
       </c>
       <c r="B5" t="n">
-        <v>91172</v>
+        <v>78546</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1503</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>878958</v>
+        <v>878975</v>
       </c>
       <c r="R5" t="n">
-        <v>7377740</v>
+        <v>7377725</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>

--- a/artfynd/A 60484-2024 artfynd.xlsx
+++ b/artfynd/A 60484-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124464181</v>
+        <v>124464173</v>
       </c>
       <c r="B2" t="n">
-        <v>78810</v>
+        <v>92490</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>878962</v>
+        <v>879013</v>
       </c>
       <c r="R2" t="n">
-        <v>7377739</v>
+        <v>7377725</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124464179</v>
+        <v>124464175</v>
       </c>
       <c r="B3" t="n">
-        <v>91172</v>
+        <v>78546</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1503</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>878958</v>
+        <v>878975</v>
       </c>
       <c r="R3" t="n">
-        <v>7377740</v>
+        <v>7377725</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124464173</v>
+        <v>124464181</v>
       </c>
       <c r="B4" t="n">
-        <v>92490</v>
+        <v>78810</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>879013</v>
+        <v>878962</v>
       </c>
       <c r="R4" t="n">
-        <v>7377725</v>
+        <v>7377739</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124464175</v>
+        <v>124464179</v>
       </c>
       <c r="B5" t="n">
-        <v>78546</v>
+        <v>91172</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>1503</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>878975</v>
+        <v>878958</v>
       </c>
       <c r="R5" t="n">
-        <v>7377725</v>
+        <v>7377740</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>

--- a/artfynd/A 60484-2024 artfynd.xlsx
+++ b/artfynd/A 60484-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124464173</v>
+        <v>124464179</v>
       </c>
       <c r="B2" t="n">
-        <v>92490</v>
+        <v>91172</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2079</v>
+        <v>1503</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>879013</v>
+        <v>878958</v>
       </c>
       <c r="R2" t="n">
-        <v>7377725</v>
+        <v>7377740</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124464181</v>
+        <v>124464173</v>
       </c>
       <c r="B4" t="n">
-        <v>78810</v>
+        <v>92490</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>878962</v>
+        <v>879013</v>
       </c>
       <c r="R4" t="n">
-        <v>7377739</v>
+        <v>7377725</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124464179</v>
+        <v>124464181</v>
       </c>
       <c r="B5" t="n">
-        <v>91172</v>
+        <v>78810</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>878958</v>
+        <v>878962</v>
       </c>
       <c r="R5" t="n">
-        <v>7377740</v>
+        <v>7377739</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>

--- a/artfynd/A 60484-2024 artfynd.xlsx
+++ b/artfynd/A 60484-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124464179</v>
+        <v>124464173</v>
       </c>
       <c r="B2" t="n">
-        <v>91172</v>
+        <v>92490</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1503</v>
+        <v>2079</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>878958</v>
+        <v>879013</v>
       </c>
       <c r="R2" t="n">
-        <v>7377740</v>
+        <v>7377725</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124464173</v>
+        <v>124464179</v>
       </c>
       <c r="B4" t="n">
-        <v>92490</v>
+        <v>91172</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2079</v>
+        <v>1503</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>879013</v>
+        <v>878958</v>
       </c>
       <c r="R4" t="n">
-        <v>7377725</v>
+        <v>7377740</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>

--- a/artfynd/A 60484-2024 artfynd.xlsx
+++ b/artfynd/A 60484-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124464173</v>
+        <v>124464181</v>
       </c>
       <c r="B2" t="n">
-        <v>92490</v>
+        <v>78810</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>879013</v>
+        <v>878962</v>
       </c>
       <c r="R2" t="n">
-        <v>7377725</v>
+        <v>7377739</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124464175</v>
+        <v>124464173</v>
       </c>
       <c r="B3" t="n">
-        <v>78546</v>
+        <v>92490</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>2079</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,7 +817,7 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>878975</v>
+        <v>879013</v>
       </c>
       <c r="R3" t="n">
         <v>7377725</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124464181</v>
+        <v>124464175</v>
       </c>
       <c r="B5" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>878962</v>
+        <v>878975</v>
       </c>
       <c r="R5" t="n">
-        <v>7377739</v>
+        <v>7377725</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>

--- a/artfynd/A 60484-2024 artfynd.xlsx
+++ b/artfynd/A 60484-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124464173</v>
+        <v>124464175</v>
       </c>
       <c r="B3" t="n">
-        <v>92490</v>
+        <v>78546</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2079</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,7 +817,7 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>879013</v>
+        <v>878975</v>
       </c>
       <c r="R3" t="n">
         <v>7377725</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124464175</v>
+        <v>124464173</v>
       </c>
       <c r="B5" t="n">
-        <v>78546</v>
+        <v>92490</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>2079</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,7 +1021,7 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>878975</v>
+        <v>879013</v>
       </c>
       <c r="R5" t="n">
         <v>7377725</v>
@@ -1080,6 +1080,618 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>125110074</v>
+      </c>
+      <c r="B6" t="n">
+        <v>90934</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>3242</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Vitplätt</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Chaetodermella luna</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Pölkkyjänkkä, Nb</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>879141</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7377720</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Hietaniemi</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk, Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>125110084</v>
+      </c>
+      <c r="B7" t="n">
+        <v>92490</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>2079</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Nordtagging</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Odonticium romellii</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(S.Lundell) Parmasto</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Pölkkyjänkkä, Nb</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>879074</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7377736</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Hietaniemi</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk, Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>125110088</v>
+      </c>
+      <c r="B8" t="n">
+        <v>78547</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Pölkkyjänkkä, Nb</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>879053</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7377740</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Hietaniemi</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk, Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>125110095</v>
+      </c>
+      <c r="B9" t="n">
+        <v>92293</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Pölkkyjänkkä, Nb</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>879054</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7377720</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Hietaniemi</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk, Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>125110086</v>
+      </c>
+      <c r="B10" t="n">
+        <v>92490</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>2079</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Nordtagging</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Odonticium romellii</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(S.Lundell) Parmasto</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Pölkkyjänkkä, Nb</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>879137</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7377724</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Hietaniemi</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk, Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>125110079</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79795</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Pölkkyjänkkä, Nb</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>879156</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7377742</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Hietaniemi</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk, Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 60484-2024 artfynd.xlsx
+++ b/artfynd/A 60484-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124464181</v>
+        <v>124464175</v>
       </c>
       <c r="B2" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>878962</v>
+        <v>878975</v>
       </c>
       <c r="R2" t="n">
-        <v>7377739</v>
+        <v>7377725</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124464175</v>
+        <v>124464173</v>
       </c>
       <c r="B3" t="n">
-        <v>78546</v>
+        <v>92490</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>2079</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,7 +817,7 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>878975</v>
+        <v>879013</v>
       </c>
       <c r="R3" t="n">
         <v>7377725</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124464173</v>
+        <v>124464181</v>
       </c>
       <c r="B5" t="n">
-        <v>92490</v>
+        <v>78810</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>879013</v>
+        <v>878962</v>
       </c>
       <c r="R5" t="n">
-        <v>7377725</v>
+        <v>7377739</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125110074</v>
+        <v>125110095</v>
       </c>
       <c r="B6" t="n">
-        <v>90934</v>
+        <v>92293</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3242</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,7 +1123,7 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>879141</v>
+        <v>879054</v>
       </c>
       <c r="R6" t="n">
         <v>7377720</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125110084</v>
+        <v>125110079</v>
       </c>
       <c r="B7" t="n">
-        <v>92490</v>
+        <v>79795</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2079</v>
+        <v>6456</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>879074</v>
+        <v>879156</v>
       </c>
       <c r="R7" t="n">
-        <v>7377736</v>
+        <v>7377742</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125110088</v>
+        <v>125110084</v>
       </c>
       <c r="B8" t="n">
-        <v>78547</v>
+        <v>92490</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>2079</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>879053</v>
+        <v>879074</v>
       </c>
       <c r="R8" t="n">
-        <v>7377740</v>
+        <v>7377736</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125110095</v>
+        <v>125110074</v>
       </c>
       <c r="B9" t="n">
-        <v>92293</v>
+        <v>90934</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,25 +1401,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>3242</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,7 +1429,7 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>879054</v>
+        <v>879141</v>
       </c>
       <c r="R9" t="n">
         <v>7377720</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125110079</v>
+        <v>125110088</v>
       </c>
       <c r="B11" t="n">
-        <v>79795</v>
+        <v>78547</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1605,25 +1605,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6456</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>879156</v>
+        <v>879053</v>
       </c>
       <c r="R11" t="n">
-        <v>7377742</v>
+        <v>7377740</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>

--- a/artfynd/A 60484-2024 artfynd.xlsx
+++ b/artfynd/A 60484-2024 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124464173</v>
+        <v>124464181</v>
       </c>
       <c r="B3" t="n">
-        <v>92490</v>
+        <v>78810</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>879013</v>
+        <v>878962</v>
       </c>
       <c r="R3" t="n">
-        <v>7377725</v>
+        <v>7377739</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124464179</v>
+        <v>124464173</v>
       </c>
       <c r="B4" t="n">
-        <v>91172</v>
+        <v>92490</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1503</v>
+        <v>2079</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>878958</v>
+        <v>879013</v>
       </c>
       <c r="R4" t="n">
-        <v>7377740</v>
+        <v>7377725</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124464181</v>
+        <v>124464179</v>
       </c>
       <c r="B5" t="n">
-        <v>78810</v>
+        <v>91172</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>878962</v>
+        <v>878958</v>
       </c>
       <c r="R5" t="n">
-        <v>7377739</v>
+        <v>7377740</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125110095</v>
+        <v>125110074</v>
       </c>
       <c r="B6" t="n">
-        <v>92293</v>
+        <v>90934</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>3242</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,7 +1123,7 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>879054</v>
+        <v>879141</v>
       </c>
       <c r="R6" t="n">
         <v>7377720</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125110079</v>
+        <v>125110095</v>
       </c>
       <c r="B7" t="n">
-        <v>79795</v>
+        <v>92293</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6456</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>879156</v>
+        <v>879054</v>
       </c>
       <c r="R7" t="n">
-        <v>7377742</v>
+        <v>7377720</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125110074</v>
+        <v>125110088</v>
       </c>
       <c r="B9" t="n">
-        <v>90934</v>
+        <v>78547</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3242</v>
+        <v>228912</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>879141</v>
+        <v>879053</v>
       </c>
       <c r="R9" t="n">
-        <v>7377720</v>
+        <v>7377740</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125110086</v>
+        <v>125110079</v>
       </c>
       <c r="B10" t="n">
-        <v>92490</v>
+        <v>79795</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1503,25 +1503,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2079</v>
+        <v>6456</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>879137</v>
+        <v>879156</v>
       </c>
       <c r="R10" t="n">
-        <v>7377724</v>
+        <v>7377742</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125110088</v>
+        <v>125110086</v>
       </c>
       <c r="B11" t="n">
-        <v>78547</v>
+        <v>92490</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>2079</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>879053</v>
+        <v>879137</v>
       </c>
       <c r="R11" t="n">
-        <v>7377740</v>
+        <v>7377724</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>

--- a/artfynd/A 60484-2024 artfynd.xlsx
+++ b/artfynd/A 60484-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124464175</v>
+        <v>124464181</v>
       </c>
       <c r="B2" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>878975</v>
+        <v>878962</v>
       </c>
       <c r="R2" t="n">
-        <v>7377725</v>
+        <v>7377739</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124464181</v>
+        <v>124464173</v>
       </c>
       <c r="B3" t="n">
-        <v>78810</v>
+        <v>92490</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>878962</v>
+        <v>879013</v>
       </c>
       <c r="R3" t="n">
-        <v>7377739</v>
+        <v>7377725</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124464173</v>
+        <v>124464179</v>
       </c>
       <c r="B4" t="n">
-        <v>92490</v>
+        <v>91172</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2079</v>
+        <v>1503</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>879013</v>
+        <v>878958</v>
       </c>
       <c r="R4" t="n">
-        <v>7377725</v>
+        <v>7377740</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124464179</v>
+        <v>124464175</v>
       </c>
       <c r="B5" t="n">
-        <v>91172</v>
+        <v>78546</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1503</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>878958</v>
+        <v>878975</v>
       </c>
       <c r="R5" t="n">
-        <v>7377740</v>
+        <v>7377725</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125110074</v>
+        <v>125110095</v>
       </c>
       <c r="B6" t="n">
-        <v>90934</v>
+        <v>92293</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3242</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,7 +1123,7 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>879141</v>
+        <v>879054</v>
       </c>
       <c r="R6" t="n">
         <v>7377720</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125110095</v>
+        <v>125110086</v>
       </c>
       <c r="B7" t="n">
-        <v>92293</v>
+        <v>92490</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>879054</v>
+        <v>879137</v>
       </c>
       <c r="R7" t="n">
-        <v>7377720</v>
+        <v>7377724</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125110084</v>
+        <v>125110074</v>
       </c>
       <c r="B8" t="n">
-        <v>92490</v>
+        <v>90934</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2079</v>
+        <v>3242</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>879074</v>
+        <v>879141</v>
       </c>
       <c r="R8" t="n">
-        <v>7377736</v>
+        <v>7377720</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1593,7 +1593,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125110086</v>
+        <v>125110084</v>
       </c>
       <c r="B11" t="n">
         <v>92490</v>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>879137</v>
+        <v>879074</v>
       </c>
       <c r="R11" t="n">
-        <v>7377724</v>
+        <v>7377736</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>

--- a/artfynd/A 60484-2024 artfynd.xlsx
+++ b/artfynd/A 60484-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124464181</v>
+        <v>124464179</v>
       </c>
       <c r="B2" t="n">
-        <v>78810</v>
+        <v>91172</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>878962</v>
+        <v>878958</v>
       </c>
       <c r="R2" t="n">
-        <v>7377739</v>
+        <v>7377740</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124464173</v>
+        <v>124464181</v>
       </c>
       <c r="B3" t="n">
-        <v>92490</v>
+        <v>78810</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>879013</v>
+        <v>878962</v>
       </c>
       <c r="R3" t="n">
-        <v>7377725</v>
+        <v>7377739</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124464179</v>
+        <v>124464173</v>
       </c>
       <c r="B4" t="n">
-        <v>91172</v>
+        <v>92490</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1503</v>
+        <v>2079</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>878958</v>
+        <v>879013</v>
       </c>
       <c r="R4" t="n">
-        <v>7377740</v>
+        <v>7377725</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125110095</v>
+        <v>125110074</v>
       </c>
       <c r="B6" t="n">
-        <v>92293</v>
+        <v>90934</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>3242</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,7 +1123,7 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>879054</v>
+        <v>879141</v>
       </c>
       <c r="R6" t="n">
         <v>7377720</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125110074</v>
+        <v>125110079</v>
       </c>
       <c r="B8" t="n">
-        <v>90934</v>
+        <v>79795</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,25 +1299,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3242</v>
+        <v>6456</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>879141</v>
+        <v>879156</v>
       </c>
       <c r="R8" t="n">
-        <v>7377720</v>
+        <v>7377742</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125110079</v>
+        <v>125110084</v>
       </c>
       <c r="B10" t="n">
-        <v>79795</v>
+        <v>92490</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1503,25 +1503,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6456</v>
+        <v>2079</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>879156</v>
+        <v>879074</v>
       </c>
       <c r="R10" t="n">
-        <v>7377742</v>
+        <v>7377736</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125110084</v>
+        <v>125110095</v>
       </c>
       <c r="B11" t="n">
-        <v>92490</v>
+        <v>92293</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1605,25 +1605,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>879074</v>
+        <v>879054</v>
       </c>
       <c r="R11" t="n">
-        <v>7377736</v>
+        <v>7377720</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>

--- a/artfynd/A 60484-2024 artfynd.xlsx
+++ b/artfynd/A 60484-2024 artfynd.xlsx
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124464173</v>
+        <v>124464175</v>
       </c>
       <c r="B4" t="n">
-        <v>92490</v>
+        <v>78546</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2079</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,7 +919,7 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>879013</v>
+        <v>878975</v>
       </c>
       <c r="R4" t="n">
         <v>7377725</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124464175</v>
+        <v>124464173</v>
       </c>
       <c r="B5" t="n">
-        <v>78546</v>
+        <v>92490</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>2079</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,7 +1021,7 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>878975</v>
+        <v>879013</v>
       </c>
       <c r="R5" t="n">
         <v>7377725</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125110074</v>
+        <v>125110084</v>
       </c>
       <c r="B6" t="n">
-        <v>90934</v>
+        <v>92490</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3242</v>
+        <v>2079</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>879141</v>
+        <v>879074</v>
       </c>
       <c r="R6" t="n">
-        <v>7377720</v>
+        <v>7377736</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125110086</v>
+        <v>125110074</v>
       </c>
       <c r="B7" t="n">
-        <v>92490</v>
+        <v>90934</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2079</v>
+        <v>3242</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>879137</v>
+        <v>879141</v>
       </c>
       <c r="R7" t="n">
-        <v>7377724</v>
+        <v>7377720</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125110079</v>
+        <v>125110086</v>
       </c>
       <c r="B8" t="n">
-        <v>79795</v>
+        <v>92490</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,25 +1299,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6456</v>
+        <v>2079</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>879156</v>
+        <v>879137</v>
       </c>
       <c r="R8" t="n">
-        <v>7377742</v>
+        <v>7377724</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125110088</v>
+        <v>125110095</v>
       </c>
       <c r="B9" t="n">
-        <v>78547</v>
+        <v>92293</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,25 +1401,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>879053</v>
+        <v>879054</v>
       </c>
       <c r="R9" t="n">
-        <v>7377740</v>
+        <v>7377720</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125110084</v>
+        <v>125110088</v>
       </c>
       <c r="B10" t="n">
-        <v>92490</v>
+        <v>78547</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,21 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2079</v>
+        <v>228912</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>879074</v>
+        <v>879053</v>
       </c>
       <c r="R10" t="n">
-        <v>7377736</v>
+        <v>7377740</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125110095</v>
+        <v>125110079</v>
       </c>
       <c r="B11" t="n">
-        <v>92293</v>
+        <v>79795</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>6456</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>879054</v>
+        <v>879156</v>
       </c>
       <c r="R11" t="n">
-        <v>7377720</v>
+        <v>7377742</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>

--- a/artfynd/A 60484-2024 artfynd.xlsx
+++ b/artfynd/A 60484-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124464179</v>
+        <v>124464173</v>
       </c>
       <c r="B2" t="n">
-        <v>91172</v>
+        <v>92490</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1503</v>
+        <v>2079</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>878958</v>
+        <v>879013</v>
       </c>
       <c r="R2" t="n">
-        <v>7377740</v>
+        <v>7377725</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124464173</v>
+        <v>124464179</v>
       </c>
       <c r="B5" t="n">
-        <v>92490</v>
+        <v>91172</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2079</v>
+        <v>1503</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>879013</v>
+        <v>878958</v>
       </c>
       <c r="R5" t="n">
-        <v>7377725</v>
+        <v>7377740</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>

--- a/artfynd/A 60484-2024 artfynd.xlsx
+++ b/artfynd/A 60484-2024 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124464181</v>
+        <v>124464175</v>
       </c>
       <c r="B3" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>878962</v>
+        <v>878975</v>
       </c>
       <c r="R3" t="n">
-        <v>7377739</v>
+        <v>7377725</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124464175</v>
+        <v>124464179</v>
       </c>
       <c r="B4" t="n">
-        <v>78546</v>
+        <v>91172</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>1503</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>878975</v>
+        <v>878958</v>
       </c>
       <c r="R4" t="n">
-        <v>7377725</v>
+        <v>7377740</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124464179</v>
+        <v>124464181</v>
       </c>
       <c r="B5" t="n">
-        <v>91172</v>
+        <v>78810</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>878958</v>
+        <v>878962</v>
       </c>
       <c r="R5" t="n">
-        <v>7377740</v>
+        <v>7377739</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125110074</v>
+        <v>125110086</v>
       </c>
       <c r="B7" t="n">
-        <v>90934</v>
+        <v>92490</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3242</v>
+        <v>2079</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>879141</v>
+        <v>879137</v>
       </c>
       <c r="R7" t="n">
-        <v>7377720</v>
+        <v>7377724</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125110086</v>
+        <v>125110079</v>
       </c>
       <c r="B8" t="n">
-        <v>92490</v>
+        <v>79795</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,25 +1299,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2079</v>
+        <v>6456</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>879137</v>
+        <v>879156</v>
       </c>
       <c r="R8" t="n">
-        <v>7377724</v>
+        <v>7377742</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125110095</v>
+        <v>125110074</v>
       </c>
       <c r="B9" t="n">
-        <v>92293</v>
+        <v>90934</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,25 +1401,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>3242</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,7 +1429,7 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>879054</v>
+        <v>879141</v>
       </c>
       <c r="R9" t="n">
         <v>7377720</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125110088</v>
+        <v>125110095</v>
       </c>
       <c r="B10" t="n">
-        <v>78547</v>
+        <v>92293</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1503,25 +1503,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>879053</v>
+        <v>879054</v>
       </c>
       <c r="R10" t="n">
-        <v>7377740</v>
+        <v>7377720</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125110079</v>
+        <v>125110088</v>
       </c>
       <c r="B11" t="n">
-        <v>79795</v>
+        <v>78547</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1605,25 +1605,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6456</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>879156</v>
+        <v>879053</v>
       </c>
       <c r="R11" t="n">
-        <v>7377742</v>
+        <v>7377740</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>

--- a/artfynd/A 60484-2024 artfynd.xlsx
+++ b/artfynd/A 60484-2024 artfynd.xlsx
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125110084</v>
+        <v>125110079</v>
       </c>
       <c r="B6" t="n">
-        <v>92490</v>
+        <v>79795</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2079</v>
+        <v>6456</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>879074</v>
+        <v>879156</v>
       </c>
       <c r="R6" t="n">
-        <v>7377736</v>
+        <v>7377742</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125110086</v>
+        <v>125110095</v>
       </c>
       <c r="B7" t="n">
-        <v>92490</v>
+        <v>92293</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>879137</v>
+        <v>879054</v>
       </c>
       <c r="R7" t="n">
-        <v>7377724</v>
+        <v>7377720</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125110079</v>
+        <v>125110086</v>
       </c>
       <c r="B8" t="n">
-        <v>79795</v>
+        <v>92490</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,25 +1299,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6456</v>
+        <v>2079</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>879156</v>
+        <v>879137</v>
       </c>
       <c r="R8" t="n">
-        <v>7377742</v>
+        <v>7377724</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125110095</v>
+        <v>125110088</v>
       </c>
       <c r="B10" t="n">
-        <v>92293</v>
+        <v>78547</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1503,25 +1503,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>879054</v>
+        <v>879053</v>
       </c>
       <c r="R10" t="n">
-        <v>7377720</v>
+        <v>7377740</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125110088</v>
+        <v>125110084</v>
       </c>
       <c r="B11" t="n">
-        <v>78547</v>
+        <v>92490</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>2079</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>879053</v>
+        <v>879074</v>
       </c>
       <c r="R11" t="n">
-        <v>7377740</v>
+        <v>7377736</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>

--- a/artfynd/A 60484-2024 artfynd.xlsx
+++ b/artfynd/A 60484-2024 artfynd.xlsx
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125110079</v>
+        <v>125110074</v>
       </c>
       <c r="B6" t="n">
-        <v>79795</v>
+        <v>91088</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6456</v>
+        <v>3242</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>879156</v>
+        <v>879141</v>
       </c>
       <c r="R6" t="n">
-        <v>7377742</v>
+        <v>7377720</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125110095</v>
+        <v>125110086</v>
       </c>
       <c r="B7" t="n">
-        <v>92293</v>
+        <v>92646</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>879054</v>
+        <v>879137</v>
       </c>
       <c r="R7" t="n">
-        <v>7377720</v>
+        <v>7377724</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125110086</v>
+        <v>125110088</v>
       </c>
       <c r="B8" t="n">
-        <v>92490</v>
+        <v>78684</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2079</v>
+        <v>228912</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>879137</v>
+        <v>879053</v>
       </c>
       <c r="R8" t="n">
-        <v>7377724</v>
+        <v>7377740</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125110074</v>
+        <v>125110079</v>
       </c>
       <c r="B9" t="n">
-        <v>90934</v>
+        <v>79932</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,25 +1401,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3242</v>
+        <v>6456</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>879141</v>
+        <v>879156</v>
       </c>
       <c r="R9" t="n">
-        <v>7377720</v>
+        <v>7377742</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125110088</v>
+        <v>125110084</v>
       </c>
       <c r="B10" t="n">
-        <v>78547</v>
+        <v>92646</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,21 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>2079</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>879053</v>
+        <v>879074</v>
       </c>
       <c r="R10" t="n">
-        <v>7377740</v>
+        <v>7377736</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125110084</v>
+        <v>125110095</v>
       </c>
       <c r="B11" t="n">
-        <v>92490</v>
+        <v>92448</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1605,25 +1605,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>879074</v>
+        <v>879054</v>
       </c>
       <c r="R11" t="n">
-        <v>7377736</v>
+        <v>7377720</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>

--- a/artfynd/A 60484-2024 artfynd.xlsx
+++ b/artfynd/A 60484-2024 artfynd.xlsx
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125110074</v>
+        <v>125110079</v>
       </c>
       <c r="B6" t="n">
-        <v>91088</v>
+        <v>79932</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3242</v>
+        <v>6456</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>879141</v>
+        <v>879156</v>
       </c>
       <c r="R6" t="n">
-        <v>7377720</v>
+        <v>7377742</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125110086</v>
+        <v>125110095</v>
       </c>
       <c r="B7" t="n">
-        <v>92646</v>
+        <v>92448</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>879137</v>
+        <v>879054</v>
       </c>
       <c r="R7" t="n">
-        <v>7377724</v>
+        <v>7377720</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125110088</v>
+        <v>125110084</v>
       </c>
       <c r="B8" t="n">
-        <v>78684</v>
+        <v>92646</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>2079</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>879053</v>
+        <v>879074</v>
       </c>
       <c r="R8" t="n">
-        <v>7377740</v>
+        <v>7377736</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125110079</v>
+        <v>125110088</v>
       </c>
       <c r="B9" t="n">
-        <v>79932</v>
+        <v>78684</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,25 +1401,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6456</v>
+        <v>228912</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>879156</v>
+        <v>879053</v>
       </c>
       <c r="R9" t="n">
-        <v>7377742</v>
+        <v>7377740</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1491,7 +1491,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125110084</v>
+        <v>125110086</v>
       </c>
       <c r="B10" t="n">
         <v>92646</v>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>879074</v>
+        <v>879137</v>
       </c>
       <c r="R10" t="n">
-        <v>7377736</v>
+        <v>7377724</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125110095</v>
+        <v>125110074</v>
       </c>
       <c r="B11" t="n">
-        <v>92448</v>
+        <v>91088</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1605,25 +1605,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>3242</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,7 +1633,7 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>879054</v>
+        <v>879141</v>
       </c>
       <c r="R11" t="n">
         <v>7377720</v>

--- a/artfynd/A 60484-2024 artfynd.xlsx
+++ b/artfynd/A 60484-2024 artfynd.xlsx
@@ -1083,37 +1083,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125110079</v>
+        <v>125110086</v>
       </c>
       <c r="B6" t="n">
-        <v>79932</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92700</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6456</v>
+        <v>2079</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1118,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>879156</v>
+        <v>879137</v>
       </c>
       <c r="R6" t="n">
-        <v>7377742</v>
+        <v>7377724</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1185,15 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125110095</v>
+        <v>125110079</v>
       </c>
       <c r="B7" t="n">
-        <v>92448</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79974</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1201,21 +1191,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>6456</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>879054</v>
+        <v>879156</v>
       </c>
       <c r="R7" t="n">
-        <v>7377720</v>
+        <v>7377742</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1287,15 +1277,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125110084</v>
+        <v>125110088</v>
       </c>
       <c r="B8" t="n">
-        <v>92646</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78726</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1303,21 +1288,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2079</v>
+        <v>228912</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1312,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>879074</v>
+        <v>879053</v>
       </c>
       <c r="R8" t="n">
-        <v>7377736</v>
+        <v>7377740</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1389,15 +1374,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125110088</v>
+        <v>125110084</v>
       </c>
       <c r="B9" t="n">
-        <v>78684</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92700</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1405,21 +1385,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>2079</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1409,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>879053</v>
+        <v>879074</v>
       </c>
       <c r="R9" t="n">
-        <v>7377740</v>
+        <v>7377736</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1491,37 +1471,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125110086</v>
+        <v>125110095</v>
       </c>
       <c r="B10" t="n">
-        <v>92646</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92502</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1506,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>879137</v>
+        <v>879054</v>
       </c>
       <c r="R10" t="n">
-        <v>7377724</v>
+        <v>7377720</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1596,12 +1571,7 @@
         <v>125110074</v>
       </c>
       <c r="B11" t="n">
-        <v>91088</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91142</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
